--- a/backend/storage/output/excel/scr-station/Rail_Madad_Report_6_SCR_Station_Unsatisfactory_13-07-2026.xlsx
+++ b/backend/storage/output/excel/scr-station/Rail_Madad_Report_6_SCR_Station_Unsatisfactory_13-07-2026.xlsx
@@ -34,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +42,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +674,147 @@
       <c r="Y2" t="inlineStr">
         <is>
           <t>Meal replaced</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>2026071304468</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 10:02</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>GLA</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>CHG</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>2026071303177</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 08:07</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>WL</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>CHG</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>2026071301678</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>13-07-26 05:26</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>KCG</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Catering &amp; Vending Services</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Overcharging</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>CML</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
     </row>
